--- a/data/trans_orig/IP07C14-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07C14-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de preocuparse con su aspecto en 2007 (tasa de respuesta: 89,69%)</t>
+          <t>Menores según la frecuencia de preocuparse por su aspecto en 2007 (tasa de respuesta: 89,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7822</t>
+          <t>7775</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18459</t>
+          <t>18429</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4241</t>
+          <t>4035</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12816</t>
+          <t>12817</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13979</t>
+          <t>14792</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27724</t>
+          <t>27669</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,05%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7653</t>
+          <t>7646</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>18405</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4159</t>
+          <t>4616</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13387</t>
+          <t>13310</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14109</t>
+          <t>14393</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27958</t>
+          <t>28066</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,37%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14363</t>
+          <t>14523</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25963</t>
+          <t>26534</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16770</t>
+          <t>16737</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29618</t>
+          <t>29345</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>34097</t>
+          <t>34616</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>51580</t>
+          <t>51579</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2186</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9637</t>
+          <t>9185</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9693</t>
+          <t>9994</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20739</t>
+          <t>20823</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13842</t>
+          <t>14116</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27253</t>
+          <t>26803</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,36%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12135</t>
+          <t>12181</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9573</t>
+          <t>9735</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21272</t>
+          <t>20607</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15058</t>
+          <t>16734</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29731</t>
+          <t>30451</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>24,27%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10548</t>
+          <t>10879</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21300</t>
+          <t>22152</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4468</t>
+          <t>4641</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13832</t>
+          <t>13563</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17302</t>
+          <t>17496</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31749</t>
+          <t>31545</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,61%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14931</t>
+          <t>14973</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28022</t>
+          <t>27245</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8020</t>
+          <t>8510</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19547</t>
+          <t>19214</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26257</t>
+          <t>25752</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>43262</t>
+          <t>43570</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,94%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25176</t>
+          <t>24710</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39779</t>
+          <t>39234</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20757</t>
+          <t>20657</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>34867</t>
+          <t>34291</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>49772</t>
+          <t>48983</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>69440</t>
+          <t>69571</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,63%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6360</t>
+          <t>6212</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15960</t>
+          <t>15330</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9212</t>
+          <t>9091</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19895</t>
+          <t>20031</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17102</t>
+          <t>16916</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31523</t>
+          <t>31697</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,69%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14660</t>
+          <t>14415</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27007</t>
+          <t>26952</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21140</t>
+          <t>20958</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34811</t>
+          <t>34375</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>39731</t>
+          <t>39052</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>58550</t>
+          <t>57605</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,33%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8361</t>
+          <t>8644</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18815</t>
+          <t>18481</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8435</t>
+          <t>8255</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19313</t>
+          <t>18712</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19547</t>
+          <t>19428</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34376</t>
+          <t>33905</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>28,97%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5440</t>
+          <t>5874</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14019</t>
+          <t>14393</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6874</t>
+          <t>7135</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16770</t>
+          <t>16710</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14974</t>
+          <t>14721</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>27892</t>
+          <t>27130</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,18%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11685</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21902</t>
+          <t>21651</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13368</t>
+          <t>14353</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25309</t>
+          <t>25129</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>28181</t>
+          <t>27929</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>43279</t>
+          <t>43684</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>37,33%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4820</t>
+          <t>4697</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12947</t>
+          <t>12975</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2930</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10550</t>
+          <t>10749</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9615</t>
+          <t>9487</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20594</t>
+          <t>20038</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,12%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4976</t>
+          <t>4642</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13523</t>
+          <t>13280</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6998</t>
+          <t>7620</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16415</t>
+          <t>16867</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13718</t>
+          <t>13966</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>25623</t>
+          <t>26264</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,44%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13506</t>
+          <t>13514</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26636</t>
+          <t>26457</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8004</t>
+          <t>7812</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18724</t>
+          <t>18831</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25131</t>
+          <t>25314</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>42400</t>
+          <t>42355</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,45%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>7104</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18403</t>
+          <t>18327</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9460</t>
+          <t>9155</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>21716</t>
+          <t>20663</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>19678</t>
+          <t>19758</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>35461</t>
+          <t>36790</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>22,1%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18815</t>
+          <t>18579</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>33825</t>
+          <t>32722</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>16594</t>
+          <t>16308</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>30403</t>
+          <t>29815</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>39025</t>
+          <t>38455</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>57730</t>
+          <t>57994</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,84%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2307</t>
+          <t>2299</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>10746</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9240</t>
+          <t>9143</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20145</t>
+          <t>20561</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14078</t>
+          <t>13489</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>27507</t>
+          <t>27735</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,66%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9231</t>
+          <t>8718</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21581</t>
+          <t>21458</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>17824</t>
+          <t>17498</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>30490</t>
+          <t>31020</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>30038</t>
+          <t>29545</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>47687</t>
+          <t>47827</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,74%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>50273</t>
+          <t>50092</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>72323</t>
+          <t>72302</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>33039</t>
+          <t>33178</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>52132</t>
+          <t>52684</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>89260</t>
+          <t>87430</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>118651</t>
+          <t>118267</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,75%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>45469</t>
+          <t>45697</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>66721</t>
+          <t>66560</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>37504</t>
+          <t>37244</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>57913</t>
+          <t>57769</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>86785</t>
+          <t>88796</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>117286</t>
+          <t>117461</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,61%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>82136</t>
+          <t>82497</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>107090</t>
+          <t>106066</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>80712</t>
+          <t>80025</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>105459</t>
+          <t>105533</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>169017</t>
+          <t>168323</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>206677</t>
+          <t>203814</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,03%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>21917</t>
+          <t>22024</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>39096</t>
+          <t>38148</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>39729</t>
+          <t>39308</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>59313</t>
+          <t>59497</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>66390</t>
+          <t>65180</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>92731</t>
+          <t>91277</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>41273</t>
+          <t>40856</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>61942</t>
+          <t>62037</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>65491</t>
+          <t>65032</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>89669</t>
+          <t>89033</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>112950</t>
+          <t>112741</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>145094</t>
+          <t>144704</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,16%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de preocuparse con su aspecto en 2012 (tasa de respuesta: 95,52%)</t>
+          <t>Menores según la frecuencia de preocuparse por su aspecto en 2012 (tasa de respuesta: 95,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10383</t>
+          <t>10075</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21859</t>
+          <t>21654</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4871</t>
+          <t>4912</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13972</t>
+          <t>14075</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17016</t>
+          <t>17752</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32373</t>
+          <t>32893</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,29%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7107</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17624</t>
+          <t>17649</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13569</t>
+          <t>13560</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13935</t>
+          <t>13542</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27896</t>
+          <t>26984</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>19,93%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10030</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21471</t>
+          <t>20810</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15295</t>
+          <t>15802</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28911</t>
+          <t>27986</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>28556</t>
+          <t>27405</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>46018</t>
+          <t>44755</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,05%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7612</t>
+          <t>7378</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18136</t>
+          <t>18096</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12485</t>
+          <t>11858</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24609</t>
+          <t>24555</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22418</t>
+          <t>22156</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38923</t>
+          <t>38902</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,73%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5499</t>
+          <t>5138</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14972</t>
+          <t>14975</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10302</t>
+          <t>10257</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22458</t>
+          <t>22034</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>17553</t>
+          <t>17750</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32584</t>
+          <t>33366</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,64%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11891</t>
+          <t>12246</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25083</t>
+          <t>24374</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14135</t>
+          <t>13369</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27281</t>
+          <t>26430</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28850</t>
+          <t>29361</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46789</t>
+          <t>46439</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10346</t>
+          <t>10688</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21966</t>
+          <t>21240</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8252</t>
+          <t>8367</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19006</t>
+          <t>18788</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21047</t>
+          <t>21358</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>37370</t>
+          <t>36501</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>18,91%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22941</t>
+          <t>22275</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36916</t>
+          <t>37053</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17486</t>
+          <t>17587</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30917</t>
+          <t>30766</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>42210</t>
+          <t>43301</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>62488</t>
+          <t>61973</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,11%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12538</t>
+          <t>12222</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24489</t>
+          <t>24235</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12989</t>
+          <t>12997</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26028</t>
+          <t>25301</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27758</t>
+          <t>28204</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44981</t>
+          <t>45720</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,69%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12681</t>
+          <t>12907</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24777</t>
+          <t>25260</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13849</t>
+          <t>13963</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27025</t>
+          <t>27265</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30099</t>
+          <t>29590</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>47054</t>
+          <t>46836</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,27%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13098</t>
+          <t>13374</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25229</t>
+          <t>25145</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7758</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18147</t>
+          <t>17751</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23944</t>
+          <t>24946</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39248</t>
+          <t>40128</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>30,01%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7304</t>
+          <t>7610</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17653</t>
+          <t>17332</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>7513</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17576</t>
+          <t>17099</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17136</t>
+          <t>17201</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31123</t>
+          <t>31087</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,25%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9104</t>
+          <t>8874</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18843</t>
+          <t>19231</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15571</t>
+          <t>15971</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27784</t>
+          <t>28425</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>27908</t>
+          <t>27867</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>44069</t>
+          <t>44535</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>33,3%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>4242</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12925</t>
+          <t>12765</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1822</t>
+          <t>1703</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8151</t>
+          <t>8202</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7370</t>
+          <t>7355</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18264</t>
+          <t>17839</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7956</t>
+          <t>7555</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17470</t>
+          <t>17350</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13103</t>
+          <t>13576</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25322</t>
+          <t>25917</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>24081</t>
+          <t>23397</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>39335</t>
+          <t>39291</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,38%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19453</t>
+          <t>19727</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33763</t>
+          <t>33668</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11616</t>
+          <t>11502</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23101</t>
+          <t>23842</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33428</t>
+          <t>34093</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>52756</t>
+          <t>53483</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,58%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15729</t>
+          <t>14914</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>29644</t>
+          <t>29260</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>5937</t>
+          <t>5666</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>15751</t>
+          <t>15982</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>23772</t>
+          <t>24246</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>41452</t>
+          <t>42429</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>24,26%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>17209</t>
+          <t>17544</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>32466</t>
+          <t>32583</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21293</t>
+          <t>21199</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>35486</t>
+          <t>36891</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>41792</t>
+          <t>43075</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>63760</t>
+          <t>63678</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,41%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8054</t>
+          <t>8132</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11110</t>
+          <t>11028</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23614</t>
+          <t>23996</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13348</t>
+          <t>14007</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>28324</t>
+          <t>28209</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,13%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5117</t>
+          <t>4968</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>15091</t>
+          <t>14427</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12184</t>
+          <t>12117</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>25562</t>
+          <t>25451</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>20210</t>
+          <t>19974</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>35923</t>
+          <t>36465</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,85%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>66065</t>
+          <t>66021</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>90781</t>
+          <t>93830</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>47601</t>
+          <t>47963</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>69129</t>
+          <t>70143</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>120643</t>
+          <t>119733</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>153041</t>
+          <t>154032</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,18%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>49377</t>
+          <t>50178</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>71865</t>
+          <t>72721</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>34085</t>
+          <t>34550</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>53278</t>
+          <t>54001</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>89329</t>
+          <t>88489</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>119170</t>
+          <t>119497</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,76%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>70243</t>
+          <t>70012</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>96125</t>
+          <t>96293</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>81894</t>
+          <t>83259</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>107959</t>
+          <t>108346</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>159928</t>
+          <t>159318</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>199705</t>
+          <t>194896</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>30,59%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>30942</t>
+          <t>31563</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>50709</t>
+          <t>51908</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>45095</t>
+          <t>45642</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>69210</t>
+          <t>68929</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>84384</t>
+          <t>84170</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>114997</t>
+          <t>114899</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,04%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>39604</t>
+          <t>39197</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>60060</t>
+          <t>61487</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>61472</t>
+          <t>61223</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>87146</t>
+          <t>85366</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>106384</t>
+          <t>106102</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>137577</t>
+          <t>137342</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,56%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de preocuparse con su aspecto en 2016 (tasa de respuesta: 95,57%)</t>
+          <t>Menores según la frecuencia de preocuparse por su aspecto en 2016 (tasa de respuesta: 95,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7632</t>
+          <t>7926</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18640</t>
+          <t>19045</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t>5423</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15263</t>
+          <t>15951</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15491</t>
+          <t>15848</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31443</t>
+          <t>30902</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,16%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8492</t>
+          <t>8904</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20571</t>
+          <t>20412</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6572</t>
+          <t>6701</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17544</t>
+          <t>17265</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18148</t>
+          <t>17944</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34147</t>
+          <t>33309</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>23,89%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15191</t>
+          <t>14877</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27753</t>
+          <t>27787</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13925</t>
+          <t>13956</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27209</t>
+          <t>27737</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>31396</t>
+          <t>32800</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>50862</t>
+          <t>51609</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>37,01%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>5103</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15056</t>
+          <t>14753</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9951</t>
+          <t>10437</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22174</t>
+          <t>22547</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17112</t>
+          <t>17202</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32962</t>
+          <t>32906</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,6%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7125</t>
+          <t>7243</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17802</t>
+          <t>17632</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9565</t>
+          <t>9318</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22158</t>
+          <t>22724</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>19371</t>
+          <t>19629</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>36398</t>
+          <t>36243</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>25,99%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16942</t>
+          <t>17185</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31217</t>
+          <t>30977</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9810</t>
+          <t>9705</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21544</t>
+          <t>21054</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29635</t>
+          <t>29376</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11447</t>
+          <t>11042</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23465</t>
+          <t>23528</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15151</t>
+          <t>15025</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29078</t>
+          <t>28635</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29293</t>
+          <t>29540</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>47493</t>
+          <t>48144</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,36%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21671</t>
+          <t>21597</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36295</t>
+          <t>36129</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14970</t>
+          <t>14362</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28339</t>
+          <t>27539</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>39898</t>
+          <t>39460</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>59582</t>
+          <t>59064</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,66%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9573</t>
+          <t>9813</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20951</t>
+          <t>20732</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11753</t>
+          <t>12243</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23873</t>
+          <t>24427</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24758</t>
+          <t>23736</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41665</t>
+          <t>41048</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>19,92%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13164</t>
+          <t>13392</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25878</t>
+          <t>26645</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23031</t>
+          <t>22059</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>38018</t>
+          <t>37501</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>38633</t>
+          <t>38942</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>59325</t>
+          <t>58358</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,31%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11845</t>
+          <t>11020</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22965</t>
+          <t>22429</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9262</t>
+          <t>8911</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20975</t>
+          <t>20689</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24278</t>
+          <t>23350</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40665</t>
+          <t>39567</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>27,38%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8659</t>
+          <t>9185</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19074</t>
+          <t>19885</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8094</t>
+          <t>7959</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19332</t>
+          <t>20560</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19965</t>
+          <t>19630</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35783</t>
+          <t>35837</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,8%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9018</t>
+          <t>8888</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20222</t>
+          <t>19254</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10142</t>
+          <t>9983</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21529</t>
+          <t>21356</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>21500</t>
+          <t>21179</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>37490</t>
+          <t>36554</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,29%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6405</t>
+          <t>6469</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16266</t>
+          <t>15877</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6792</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16350</t>
+          <t>16788</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14566</t>
+          <t>14953</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28971</t>
+          <t>29893</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,68%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10333</t>
+          <t>10294</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21318</t>
+          <t>21070</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14585</t>
+          <t>14901</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>28051</t>
+          <t>27540</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>27381</t>
+          <t>27540</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>43961</t>
+          <t>44318</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,66%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14138</t>
+          <t>15048</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29575</t>
+          <t>29706</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7553</t>
+          <t>7778</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19300</t>
+          <t>19470</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25431</t>
+          <t>25966</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>43472</t>
+          <t>44105</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,68%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10226</t>
+          <t>10722</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22617</t>
+          <t>23321</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>15172</t>
+          <t>14582</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>30169</t>
+          <t>28253</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>28901</t>
+          <t>27253</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>47690</t>
+          <t>46904</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,06%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>21485</t>
+          <t>20830</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>36593</t>
+          <t>37171</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13854</t>
+          <t>13824</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>27554</t>
+          <t>27508</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>38543</t>
+          <t>38621</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>58893</t>
+          <t>59123</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,07%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11407</t>
+          <t>11424</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24461</t>
+          <t>24757</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22343</t>
+          <t>22619</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>37722</t>
+          <t>37618</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>37176</t>
+          <t>37071</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>56518</t>
+          <t>56990</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>28,02%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>14826</t>
+          <t>14489</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>28635</t>
+          <t>28735</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10958</t>
+          <t>11501</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23828</t>
+          <t>24065</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>29104</t>
+          <t>29126</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>48522</t>
+          <t>47901</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,55%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>62585</t>
+          <t>61523</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>89332</t>
+          <t>88199</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>40377</t>
+          <t>40935</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>63315</t>
+          <t>63405</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>108022</t>
+          <t>108640</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>141653</t>
+          <t>141586</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,42%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>48387</t>
+          <t>48488</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>73499</t>
+          <t>72062</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>55627</t>
+          <t>56280</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>80762</t>
+          <t>81468</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>110471</t>
+          <t>111458</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>143594</t>
+          <t>145195</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,94%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>79074</t>
+          <t>77774</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>106522</t>
+          <t>104460</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>62738</t>
+          <t>62884</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>89459</t>
+          <t>88763</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>149240</t>
+          <t>148549</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>186544</t>
+          <t>184676</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,63%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>41523</t>
+          <t>40784</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>63980</t>
+          <t>62702</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>60490</t>
+          <t>60399</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>86967</t>
+          <t>85051</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>107044</t>
+          <t>107913</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>141189</t>
+          <t>141249</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,37%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>56245</t>
+          <t>57390</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>80310</t>
+          <t>80557</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>69260</t>
+          <t>69703</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>96743</t>
+          <t>96024</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>131453</t>
+          <t>133267</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>167790</t>
+          <t>168721</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,33%</t>
         </is>
       </c>
     </row>
